--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,12 +662,190 @@
           <t>NSE:JINDALSTEL26SEP1180CE</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:18:01</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>DIXON</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>14917</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>316.2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>212.72</v>
+      </c>
+      <c r="K3" t="n">
+        <v>408.59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>464.03</v>
+      </c>
+      <c r="M3" t="n">
+        <v>537.9400000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>158</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="S3" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>62.82</v>
+      </c>
+      <c r="U3" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Consumer Durables</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>NSE:DIXON26SEP15000CE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:18:01</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>497.95</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>500</v>
+      </c>
+      <c r="I4" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K4" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="L4" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="M4" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4184</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="T4" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="U4" t="n">
+        <v>50</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26SEP500CE</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -840,12 +840,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:19:36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -840,11 +840,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-28 09:19:36</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -840,7 +840,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:22:43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -662,6 +662,11 @@
           <t>NSE:JINDALSTEL26SEP1180CE</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:24:18</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -751,6 +756,11 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:24:17</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -838,11 +848,6 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:JUBLFOOD26SEP500CE</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2026-08-28 09:22:43</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -756,11 +756,7 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-28 09:24:17</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -756,7 +756,6 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -844,6 +843,11 @@
       <c r="W4" t="inlineStr">
         <is>
           <t>NSE:JUBLFOOD26SEP500CE</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:27:25</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -756,6 +756,11 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:28:58</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -662,6 +662,16 @@
           <t>NSE:JINDALSTEL26SEP1180CE</t>
         </is>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:30:58</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>2026-08-28 09:24:18</t>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -766,11 +766,7 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2026-08-28 09:28:58</t>
-        </is>
-      </c>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -766,7 +766,11 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:36:43</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -865,6 +865,101 @@
           <t>2026-08-28 09:27:25</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:42:57</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>11867</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I5" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="K5" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="L5" t="n">
+        <v>345.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>381.34</v>
+      </c>
+      <c r="N5" t="n">
+        <v>182</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="U5" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -954,12 +954,16 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:52:14</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -964,6 +964,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-08-28 09:58:36</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -969,6 +969,101 @@
           <t>2026-08-28 09:58:36</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:23:36</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>497.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="H6" t="n">
+        <v>500</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K6" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="L6" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="N6" t="n">
+        <v>4184</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R6" t="n">
+        <v>0.653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="T6" t="n">
+        <v>51.32</v>
+      </c>
+      <c r="U6" t="n">
+        <v>50</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26SEP500CE</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1058,12 +1058,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:25:10</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1058,11 +1058,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-08-28 10:25:10</t>
-        </is>
-      </c>
+      <c r="AC6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1058,7 +1058,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-08-28 10:45:32</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC6"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1063,6 +1063,101 @@
           <t>2026-08-28 10:45:32</t>
         </is>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:03:09</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>607.65</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H7" t="n">
+        <v>610</v>
+      </c>
+      <c r="I7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K7" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="L7" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="M7" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2538</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R7" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="S7" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="T7" t="n">
+        <v>40.59</v>
+      </c>
+      <c r="U7" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>NSE:KPITTECH26SEP610PE</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,12 +1152,100 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:51:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-28 11:51:36</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>494.25</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-1.93</v>
+      </c>
+      <c r="H8" t="n">
+        <v>500</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.44</v>
+      </c>
+      <c r="K8" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="L8" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="M8" t="n">
+        <v>21.61</v>
+      </c>
+      <c r="N8" t="n">
+        <v>4184</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="T8" t="n">
+        <v>49.62</v>
+      </c>
+      <c r="U8" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>NSE:JUBLFOOD26SEP500CE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,6 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:01:20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:01:20</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:07:41</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1251,6 +1251,101 @@
           <t>2026-08-28 12:07:41</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:12:29</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BAJAJ-AUTO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>11947</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I9" t="n">
+        <v>273.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>223.32</v>
+      </c>
+      <c r="K9" t="n">
+        <v>318.49</v>
+      </c>
+      <c r="L9" t="n">
+        <v>345.42</v>
+      </c>
+      <c r="M9" t="n">
+        <v>381.34</v>
+      </c>
+      <c r="N9" t="n">
+        <v>182</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R9" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="S9" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>61.56</v>
+      </c>
+      <c r="U9" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:07:41</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1340,12 +1336,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:15:50</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:15:50</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:20:36</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1246,11 +1246,6 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:20:36</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1338,6 +1333,100 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:22:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:22:21</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SONACOMS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>805.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.62</v>
+      </c>
+      <c r="H10" t="n">
+        <v>810</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="K10" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="L10" t="n">
+        <v>32.91</v>
+      </c>
+      <c r="M10" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1225</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R10" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="S10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="T10" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="U10" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Auto Anc</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NSE:SONACOMS26SEP810CE</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,6 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:23:58</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1335,11 +1340,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:22:22</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1427,6 +1427,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>NSE:SONACOMS26SEP810CE</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:23:58</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,6 +1340,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:25:33</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,11 +1340,7 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:25:33</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,7 +1340,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:31:55</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1439,6 +1439,101 @@
           <t>2026-08-28 12:23:58</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:33:31</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>COFORGE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1994.4</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="J11" t="n">
+        <v>55.68</v>
+      </c>
+      <c r="K11" t="n">
+        <v>80.23</v>
+      </c>
+      <c r="L11" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>96.44</v>
+      </c>
+      <c r="N11" t="n">
+        <v>475</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="S11" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>73.38</v>
+      </c>
+      <c r="U11" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>NSE:COFORGE26SEP2000CE</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:23:58</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1340,11 +1336,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:31:55</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1528,12 +1519,6 @@
           <t>NSE:COFORGE26SEP2000CE</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:36:43</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,6 +1340,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:39:21</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,11 +1340,7 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:39:21</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,7 +1340,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:45:51</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,6 +1528,101 @@
           <t>NSE:COFORGE26SEP2000CE</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:50:37</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>606.9</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="H12" t="n">
+        <v>610</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="K12" t="n">
+        <v>23.19</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.29</v>
+      </c>
+      <c r="M12" t="n">
+        <v>28.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2538</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Range-Pinned</t>
+        </is>
+      </c>
+      <c r="R12" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="S12" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>40.17</v>
+      </c>
+      <c r="U12" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>NSE:KPITTECH26SEP610PE</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:36:43</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1340,11 +1336,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:45:51</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1617,12 +1608,6 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:53:55</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1334,6 +1338,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:53:55</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,11 +1340,7 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:53:55</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:53:55</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1340,7 +1336,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:58:43</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1334,6 +1338,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:58:43</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,11 +1340,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:58:43</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1615,6 +1610,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KPITTECH26SEP610PE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-28 12:59:49</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1612,11 +1612,7 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:59:49</t>
-        </is>
-      </c>
+      <c r="AC12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1612,7 +1612,11 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:12:55</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1340,6 +1340,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:14:31</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1610,11 +1615,6 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KPITTECH26SEP610PE</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:12:55</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 12:58:43</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1338,11 +1334,6 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:14:31</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,6 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1606,6 +1605,11 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KPITTECH26SEP610PE</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:20:18</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,6 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:21:56</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1605,11 +1610,6 @@
       <c r="W12" t="inlineStr">
         <is>
           <t>NSE:KPITTECH26SEP610PE</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:20:18</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:21:56</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:34:54</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:34:54</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:39:46</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,11 +1246,7 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-08-28 13:39:46</t>
-        </is>
-      </c>
+      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1246,7 +1246,6 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1334,6 +1333,11 @@
       <c r="W9" t="inlineStr">
         <is>
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:24:51</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1335,11 +1335,7 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 14:24:51</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1335,7 +1335,11 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:32:51</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1335,11 +1335,7 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-08-28 14:32:51</t>
-        </is>
-      </c>
+      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1335,7 +1335,6 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1608,6 +1607,101 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:55:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>1017.7</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1020</v>
+      </c>
+      <c r="I13" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="K13" t="n">
+        <v>41.82</v>
+      </c>
+      <c r="L13" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="M13" t="n">
+        <v>51.64</v>
+      </c>
+      <c r="N13" t="n">
+        <v>650</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>0.657</v>
+      </c>
+      <c r="S13" t="n">
+        <v>30</v>
+      </c>
+      <c r="T13" t="n">
+        <v>43.62</v>
+      </c>
+      <c r="U13" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Power</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>NSE:PREMIERENE26SEP1020PE</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1335,6 +1335,16 @@
           <t>NSE:BAJAJ-AUTO26SEP11900CE</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:55:29</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1696,12 +1706,6 @@
           <t>NSE:PREMIERENE26SEP1020PE</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1706,6 +1706,11 @@
           <t>NSE:PREMIERENE26SEP1020PE</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2026-08-28 14:56:44</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -1345,6 +1345,11 @@
           <t>Target 1 Hit</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-08-28 15:03:06</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1716,6 +1716,101 @@
           <t>2026-08-28 14:56:44</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-28 15:30:13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>9239</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9200</v>
+      </c>
+      <c r="I14" t="n">
+        <v>253.35</v>
+      </c>
+      <c r="J14" t="n">
+        <v>198.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>302.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>331.99</v>
+      </c>
+      <c r="M14" t="n">
+        <v>371.32</v>
+      </c>
+      <c r="N14" t="n">
+        <v>100</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>OI-Confirmed Momentum</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="S14" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="T14" t="n">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="U14" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>NSE:DIVISLAB26SEP9200CE</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
+++ b/backend/signal_logs/2026-08-28/signals_2026-08-28.xlsx
@@ -766,6 +766,11 @@
           <t>NSE:DIXON26SEP15000CE</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Closed down ~305.45 (-3.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
           <t>2026-08-28 09:36:43</t>
@@ -860,6 +865,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Closed up ~12.85 (+7.5% from entry)</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>2026-08-28 09:27:25</t>
@@ -1058,6 +1068,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Closed up ~12.1 (+1.3% from entry)</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
           <t>2026-08-28 10:45:32</t>
@@ -1152,6 +1167,11 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Closed up ~21.55 (+9.4% from entry)</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>2026-08-28 11:51:36</t>
@@ -1246,6 +1266,11 @@
           <t>NSE:JUBLFOOD26SEP500CE</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Closed down ~10.8 (-9.6% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1439,6 +1464,11 @@
           <t>NSE:SONACOMS26SEP810CE</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Closed flat ~25.3 (+0.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>2026-08-28 12:23:58</t>
@@ -1533,6 +1563,16 @@
           <t>NSE:COFORGE26SEP2000CE</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-28 13:58:00</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>Target 1 Hit</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1622,6 +1662,11 @@
           <t>NSE:KPITTECH26SEP610PE</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>Closed down ~17.55 (-10.9% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1711,6 +1756,11 @@
           <t>NSE:PREMIERENE26SEP1020PE</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>Closed flat ~34.8 (+0.0% from entry)</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr">
         <is>
           <t>2026-08-28 14:56:44</t>
@@ -1805,12 +1855,11 @@
           <t>NSE:DIVISLAB26SEP9200CE</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>Closed down ~249.05 (-1.7% from entry, EOD estimate)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
